--- a/docs/DB設計書.xlsx
+++ b/docs/DB設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fixie\OneDrive\デスクトップ\カレーマチアプ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E1FA42-16D5-424F-9A70-6334BAA8983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565CD3D4-6CC9-45A3-A8E4-ECF394066D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18435" yWindow="-16200" windowWidth="10470" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
   <si>
     <t>users テーブル定義</t>
   </si>
@@ -519,6 +519,38 @@
   </si>
   <si>
     <t>VARCHAR(500)</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>gender</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>age</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>性別　（任意）</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>年齢帯　（任意）</t>
+    <rPh sb="0" eb="3">
+      <t>ネンレイタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニンイ</t>
+    </rPh>
     <phoneticPr fontId="9"/>
   </si>
 </sst>
@@ -688,6 +720,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -696,9 +731,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1014,28 +1046,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1145,7 +1177,7 @@
         <v>124</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="10" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1256,40 +1288,40 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1319,28 +1351,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1601,52 +1633,52 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1664,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1677,28 +1709,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1917,92 +1949,132 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
+      <c r="G16" s="4"/>
+      <c r="H16" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+    <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" spans="1:8" ht="14" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" ht="14" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <phoneticPr fontId="9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2025,16 +2097,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="3" spans="1:8" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">

--- a/docs/DB設計書.xlsx
+++ b/docs/DB設計書.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fixie\OneDrive\デスクトップ\カレーマチアプ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565CD3D4-6CC9-45A3-A8E4-ECF394066D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EB43FC-A54E-4D42-8D6E-01A0E17DE20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18435" yWindow="-16200" windowWidth="10470" windowHeight="15585" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="-16200" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
     <sheet name="users_profile" sheetId="2" r:id="rId2"/>
     <sheet name="diagnosis_results" sheetId="3" r:id="rId3"/>
-    <sheet name="ER概要" sheetId="4" r:id="rId4"/>
+    <sheet name="questionnaire" sheetId="6" r:id="rId4"/>
+    <sheet name="ER概要" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="144">
   <si>
     <t>users テーブル定義</t>
   </si>
@@ -553,12 +554,173 @@
     </rPh>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">questionnaire </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2B4C7E"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>テーブル定義</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>診断設問を管理するテーブル</t>
+    <rPh sb="0" eb="4">
+      <t>シンダンセツモン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>questionnaire_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>INT</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>設問</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>セツモン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>questionnaire_type</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>設問</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タイプ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>diagnosis_results</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>axis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>番号に対応)</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>セツモン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>question</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>設問内容</t>
+    <rPh sb="0" eb="2">
+      <t>セツモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>reversed_score</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>スコア反転フラグ （「そう思わない」で加点）</t>
+    <rPh sb="3" eb="5">
+      <t>ハンテン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カテン</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,6 +814,44 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2B4C7E"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -693,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,6 +931,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2082,6 +2286,251 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDA2BE9-65C7-4091-B028-9ABE13F151F3}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+    </row>
+    <row r="10" spans="1:8" ht="11" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="1:8" ht="11" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" ht="11" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="1:8" ht="11" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+    </row>
+    <row r="14" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <phoneticPr fontId="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
